--- a/outbreaks/data/TPP_outbreak_diseases.xlsx
+++ b/outbreaks/data/TPP_outbreak_diseases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myfinddx-my.sharepoint.com/personal/devy_emperador_finddx_org/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Anna/Documents/GitHub/dxreadiness.data/outbreaks/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{9E3DADD1-59D6-4A2E-9D19-66F09CDC162B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4055E3AC-C26E-4510-93E7-3B16B5F586A3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6632E71C-12AB-3C40-B495-6F5441994B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EAD8D14-CA75-45A7-93F9-747D2B1467A3}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{5EAD8D14-CA75-45A7-93F9-747D2B1467A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,16 +656,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CAA870-C9B3-40D1-9734-F5C2114CBB44}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,7 +682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -693,82 +693,70 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4">
         <v>45301</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.9">
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
       <c r="D5" s="4">
         <v>45301</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D6" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -777,20 +765,26 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="D9" s="4">
         <v>45301</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -799,9 +793,9 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -810,141 +804,150 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D12" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="D13" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.9">
+    <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
       </c>
       <c r="D14" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="4">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="4">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="4">
-        <v>45301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="4">
-        <v>45301</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4">
-        <v>45301</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="D18" s="4">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="4">
-        <v>45301</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D19" s="4">
         <v>45301</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="4">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="4">
-        <v>45301</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
       <c r="D21" s="4">
         <v>45301</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E21">
+    <sortCondition ref="B2:B21"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{671C811A-3BC9-45AC-ABA3-0EE513016E94}"/>
-    <hyperlink ref="C19" r:id="rId2" xr:uid="{060B4E86-8844-4DBD-970D-E56F8E91010A}"/>
-    <hyperlink ref="C15" r:id="rId3" xr:uid="{871E2CC3-899C-4EBE-ADE7-74F2CA47B5B8}"/>
-    <hyperlink ref="C16" r:id="rId4" xr:uid="{E3AE5E7F-561A-492C-ACCD-7F6A6796D970}"/>
-    <hyperlink ref="C7" r:id="rId5" xr:uid="{429F2B8A-A1AB-47C7-AC0C-D5363BAE3BE0}"/>
+    <hyperlink ref="C13" r:id="rId1" xr:uid="{671C811A-3BC9-45AC-ABA3-0EE513016E94}"/>
+    <hyperlink ref="C20" r:id="rId2" xr:uid="{060B4E86-8844-4DBD-970D-E56F8E91010A}"/>
+    <hyperlink ref="C18" r:id="rId3" xr:uid="{871E2CC3-899C-4EBE-ADE7-74F2CA47B5B8}"/>
+    <hyperlink ref="C9" r:id="rId4" xr:uid="{E3AE5E7F-561A-492C-ACCD-7F6A6796D970}"/>
+    <hyperlink ref="C15" r:id="rId5" xr:uid="{429F2B8A-A1AB-47C7-AC0C-D5363BAE3BE0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId6"/>
@@ -954,13 +957,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E96E83-3A8E-422F-9817-1FCAA9C424C8}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="79.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="79.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -968,7 +971,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -976,7 +979,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -984,7 +987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -992,7 +995,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1025,6 +1028,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B97E08FA67D4B9408E0FC70B0A39CA3B" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1a349ade30a898d51ba6eb4ff3545c8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e92c2cad-89cf-45ba-a138-6b8dccfa7938" xmlns:ns3="99c21681-f569-4b59-99f0-5349f0a9919b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d30f1436d8a9d3e3b3863fa47ffc6b7" ns2:_="" ns3:_="">
     <xsd:import namespace="e92c2cad-89cf-45ba-a138-6b8dccfa7938"/>
@@ -1241,25 +1253,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D37A976-EA82-490D-BB3F-18B00535EA41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D37A976-EA82-490D-BB3F-18B00535EA41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="99c21681-f569-4b59-99f0-5349f0a9919b"/>
+    <ds:schemaRef ds:uri="e92c2cad-89cf-45ba-a138-6b8dccfa7938"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB2B247-2EE3-4EA1-B95F-EC3A2AC65662}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003505C1-AB94-4E79-920F-D19E9D036F37}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003505C1-AB94-4E79-920F-D19E9D036F37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB2B247-2EE3-4EA1-B95F-EC3A2AC65662}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e92c2cad-89cf-45ba-a138-6b8dccfa7938"/>
+    <ds:schemaRef ds:uri="99c21681-f569-4b59-99f0-5349f0a9919b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
